--- a/DOSSIES_MULTIFORMATO/CASA_CIVIL/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/CASA_CIVIL/dossie.xlsx
@@ -469,7 +469,11 @@
           <t>cnpj</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>19.371.471/0001-34</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -503,7 +507,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20927.09</t>
         </is>
       </c>
     </row>
@@ -521,7 +525,11 @@
           <t>faturas_exigiveis</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -529,7 +537,11 @@
           <t>faturas_prescritas</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -604,7 +616,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2020NE00721</t>
+          <t>2020NE00723</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -614,7 +626,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7712.31</v>
+        <v>1695.96</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -623,14 +635,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anulação da NE nº 00020/2020, referente ao saldo do Convênio nº 001/2016 do ( Quarto Termo Aditivo), de acordo com o Decreto nº43.042 de 18.11.2020, em virtude do encerramento do exercício 2020.</t>
+          <t>Anulação da NE nº 00021/2020, referente ao saldo do Convênio nº 001/2016 do ( Quinto Termo Aditivo), de acordo com o Decreto nº 43.042 de 18.11.2020, em virtude do encerramento do exercício 2020.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2020NE00723</t>
+          <t>2020NE00721</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -640,7 +652,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1695.96</v>
+        <v>7712.31</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -649,7 +661,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anulação da NE nº 00021/2020, referente ao saldo do Convênio nº 001/2016 do ( Quinto Termo Aditivo), de acordo com o Decreto nº 43.042 de 18.11.2020, em virtude do encerramento do exercício 2020.</t>
+          <t>Anulação da NE nº 00020/2020, referente ao saldo do Convênio nº 001/2016 do ( Quarto Termo Aditivo), de acordo com o Decreto nº43.042 de 18.11.2020, em virtude do encerramento do exercício 2020.</t>
         </is>
       </c>
     </row>
@@ -742,14 +754,10 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024NE0000579</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3/2023</t>
-        </is>
-      </c>
+          <t>2024NE0000578</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>31/07/2024</t>
@@ -765,17 +773,21 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
+          <t>ANULAÇÃO TOTAL DA NE Nº 0000533, DEVIDO DESCRIÇÃO INDEVIDA.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024NE0000578</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>2024NE0000579</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3/2023</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>31/07/2024</t>
@@ -791,7 +803,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ANULAÇÃO TOTAL DA NE Nº 0000533, DEVIDO DESCRIÇÃO INDEVIDA.</t>
+          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
         </is>
       </c>
     </row>
@@ -828,7 +840,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2019NE01223</t>
+          <t>2019NE01214</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -838,7 +850,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>24594.18</v>
+        <v>1209.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -847,7 +859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE nº00014, de acordo com o calendário de encerramento do exercício de 2019 ¿ Anexo I do Decreto nº41.554 de 26.11.2019.</t>
+          <t>Anulação parcial</t>
         </is>
       </c>
     </row>
@@ -880,7 +892,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2019NE01214</t>
+          <t>2019NE01223</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -890,7 +902,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1209.7</v>
+        <v>24594.18</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -899,14 +911,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anulação parcial</t>
+          <t>Anulação parcial da NE nº00014, de acordo com o calendário de encerramento do exercício de 2019 ¿ Anexo I do Decreto nº41.554 de 26.11.2019.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2016NE00570</t>
+          <t>2016NE00569</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -916,7 +928,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>31401.92</v>
+        <v>6498.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -932,7 +944,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2016NE00560</t>
+          <t>2016NE00568</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -942,7 +954,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3336.17</v>
+        <v>10125.33</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -951,7 +963,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Anulação total, tendo em vista o término do 3º T.A. ao Contrato nº003/2012.</t>
+          <t>Anulação parcial tendo em vista o término do Contrato nº001/2015, Instrução Normativa nº01/2016-SEF/SEFAZ.</t>
         </is>
       </c>
     </row>
@@ -984,7 +996,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2016NE00568</t>
+          <t>2016NE00560</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -994,7 +1006,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10125.33</v>
+        <v>3336.17</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1003,14 +1015,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anulação parcial tendo em vista o término do Contrato nº001/2015, Instrução Normativa nº01/2016-SEF/SEFAZ.</t>
+          <t>Anulação total, tendo em vista o término do 3º T.A. ao Contrato nº003/2012.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2016NE00569</t>
+          <t>2016NE00570</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1020,7 +1032,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6498.1</v>
+        <v>31401.92</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1114,7 +1126,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2017NE00973</t>
+          <t>2017NE00972</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1124,7 +1136,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>61071.83</v>
+        <v>68753.81</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1133,7 +1145,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Anulação parcial.</t>
+          <t>Anulação parcial</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1178,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2017NE00972</t>
+          <t>2017NE00973</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1176,7 +1188,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>68753.81</v>
+        <v>61071.83</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1185,28 +1197,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Anulação parcial</t>
+          <t>Anulação parcial.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2024NE0000792</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3/2023</t>
-        </is>
-      </c>
+          <t>2024NE0000794</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>29/10/2024</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4536.02</v>
+        <v>223778.86</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1215,24 +1223,28 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
+          <t>Correspondente à cessão por disposição, de 06 (seis) Técnicos detentores de empregos do Quadro da PRODAM, referente novembro e dezembro/2024.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2024NE0000794</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>2024NE0000792</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>3/2023</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
           <t>29/10/2024</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>223778.86</v>
+        <v>4536.02</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1241,7 +1253,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Correspondente à cessão por disposição, de 06 (seis) Técnicos detentores de empregos do Quadro da PRODAM, referente novembro e dezembro/2024.</t>
+          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
         </is>
       </c>
     </row>
@@ -1278,21 +1290,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2016NE00291</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3/2012</t>
-        </is>
-      </c>
+          <t>2016NE00292</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>29/07/2016</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>57450.3</v>
+        <v>32744.42</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,7 +1309,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada de prestação de serviços técnicos em telecomunicações de disponibilidade de acesso remoto à rede mundial internet</t>
+          <t>Indenizações do Ressarcimento de despesas decorrentes do Convênio nº01/2015- celebrado entre Secretaria de Estado da Casa Civil e Prodam/AM, ficando o mês de abril de 2016 sem a devida cobertura.</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1346,21 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2016NE00292</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
+          <t>2016NE00291</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>3/2012</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr">
         <is>
           <t>29/07/2016</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>32744.42</v>
+        <v>57450.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1357,7 +1369,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Indenizações do Ressarcimento de despesas decorrentes do Convênio nº01/2015- celebrado entre Secretaria de Estado da Casa Civil e Prodam/AM, ficando o mês de abril de 2016 sem a devida cobertura.</t>
+          <t>Contratação de empresa especializada de prestação de serviços técnicos em telecomunicações de disponibilidade de acesso remoto à rede mundial internet</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1488,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2018NE00843</t>
+          <t>2018NE00828</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1486,7 +1498,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>35108.52</v>
+        <v>43251.13</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1502,7 +1514,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2018NE00851</t>
+          <t>2018NE00816</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1512,7 +1524,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>258874.44</v>
+        <v>102000.48</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1521,7 +1533,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anulação parcial</t>
+          <t>Anulação Parcial</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1566,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2018NE00816</t>
+          <t>2018NE00851</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1564,7 +1576,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>102000.48</v>
+        <v>258874.44</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1573,14 +1585,14 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anulação Parcial</t>
+          <t>Anulação parcial</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2018NE00828</t>
+          <t>2018NE00843</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1590,7 +1602,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>43251.13</v>
+        <v>35108.52</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1688,7 +1700,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2019NE00139</t>
+          <t>2019NE00152</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1707,7 +1719,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Anulação total do empenho.</t>
+          <t>Convênio tem por objeto a Cessão , por disposição de técnicos detentores de empregos do Quadro de Técnicos da Prodam/AM, mês de dezembro/2018, ref. ao Segundo T. A. ao Convênio nº001/2016.</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1752,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2019NE00152</t>
+          <t>2019NE00139</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1759,7 +1771,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Convênio tem por objeto a Cessão , por disposição de técnicos detentores de empregos do Quadro de Técnicos da Prodam/AM, mês de dezembro/2018, ref. ao Segundo T. A. ao Convênio nº001/2016.</t>
+          <t>Anulação total do empenho.</t>
         </is>
       </c>
     </row>
@@ -1822,21 +1834,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2023NE0000615</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>3/2023</t>
-        </is>
-      </c>
+          <t>2023NE0000613</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>27/09/2023</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4340.69</v>
+        <v>111889.43</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1845,24 +1853,28 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
+          <t>O presente Termo Aditivo tem por objeto a prorrogação do prazo de vigência do Termo de Convênio nº001/2021, cujo objeto é a cessão, por disposição, de 06 (seis) Técnicos detentores de empregos do Quad</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2023NE0000613</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>2023NE0000615</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>3/2023</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr">
         <is>
           <t>27/09/2023</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>111889.43</v>
+        <v>4340.69</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1871,7 +1883,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>O presente Termo Aditivo tem por objeto a prorrogação do prazo de vigência do Termo de Convênio nº001/2021, cujo objeto é a cessão, por disposição, de 06 (seis) Técnicos detentores de empregos do Quad</t>
+          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
         </is>
       </c>
     </row>
@@ -1904,17 +1916,21 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2024NE0000100</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>2024NE0000099</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>3/2023</t>
+        </is>
+      </c>
       <c r="C50" t="inlineStr">
         <is>
           <t>27/02/2024</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>223778.86</v>
+        <v>8681.379999999999</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1923,28 +1939,24 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cessão, por disposição, de 06 (seis) Técnicos detentores de empregos do Quadro da PRODAM</t>
+          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2024NE0000099</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>3/2023</t>
-        </is>
-      </c>
+          <t>2024NE0000100</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
           <t>27/02/2024</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>8681.379999999999</v>
+        <v>223778.86</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1953,24 +1965,28 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
+          <t>Cessão, por disposição, de 06 (seis) Técnicos detentores de empregos do Quadro da PRODAM</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2023NE0000658</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
+          <t>2023NE0000657</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>3/2023</t>
+        </is>
+      </c>
       <c r="C52" t="inlineStr">
         <is>
           <t>26/10/2023</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>223778.86</v>
+        <v>8681.379999999999</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -1979,28 +1995,24 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cessão, por disposição, de 06 (seis) Técnicos detentores de empregos do Quadro da PRODAM ¿ Processamento de Dados Amazonas S.A para a Secretaria de Estado da Casa Civil.</t>
+          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2023NE0000657</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>3/2023</t>
-        </is>
-      </c>
+          <t>2023NE0000658</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
           <t>26/10/2023</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8681.379999999999</v>
+        <v>223778.86</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2009,7 +2021,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
+          <t>Cessão, por disposição, de 06 (seis) Técnicos detentores de empregos do Quadro da PRODAM ¿ Processamento de Dados Amazonas S.A para a Secretaria de Estado da Casa Civil.</t>
         </is>
       </c>
     </row>
@@ -2102,21 +2114,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025NE0000638</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>3/2023</t>
-        </is>
-      </c>
+          <t>2025NE0000639</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
           <t>25/08/2025</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4784.6</v>
+        <v>104467.15</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2125,24 +2133,28 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
+          <t>Cessão por disposição, de 05(cinco) Técnicos detentores de empregos, do Quadro da PRODAM.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025NE0000639</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
+          <t>2025NE0000638</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>3/2023</t>
+        </is>
+      </c>
       <c r="C58" t="inlineStr">
         <is>
           <t>25/08/2025</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>104467.15</v>
+        <v>4784.6</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2151,28 +2163,24 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cessão por disposição, de 05(cinco) Técnicos detentores de empregos, do Quadro da PRODAM.</t>
+          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025NE0000418</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>3/2023</t>
-        </is>
-      </c>
+          <t>2025NE0000415</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
           <t>25/06/2025</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>3024.02</v>
+        <v>208934.3</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2181,24 +2189,28 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
+          <t>Cessão, por disposição, de 05 (cinco) Técnicos detentores de empregos do Quadro da PRODAM-Processamento de Dados Amazonas S.A., para a Casa Civil, pelo período de 12 (doze) meses.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025NE0000415</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
+          <t>2025NE0000418</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>3/2023</t>
+        </is>
+      </c>
       <c r="C60" t="inlineStr">
         <is>
           <t>25/06/2025</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>208934.3</v>
+        <v>3024.02</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2207,7 +2219,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cessão, por disposição, de 05 (cinco) Técnicos detentores de empregos do Quadro da PRODAM-Processamento de Dados Amazonas S.A., para a Casa Civil, pelo período de 12 (doze) meses.</t>
+          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
         </is>
       </c>
     </row>
@@ -2270,21 +2282,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025NE0000091</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>3/2023</t>
-        </is>
-      </c>
+          <t>2025NE0000092</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
           <t>25/02/2025</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>9072.040000000001</v>
+        <v>223778.86</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2293,24 +2301,28 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
+          <t>Cessão, por disposição, de 06(seis) técnicos detentores de empregos do Quadro da PRODAM.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025NE0000092</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
+          <t>2025NE0000091</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>3/2023</t>
+        </is>
+      </c>
       <c r="C64" t="inlineStr">
         <is>
           <t>25/02/2025</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>223778.86</v>
+        <v>9072.040000000001</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2319,7 +2331,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cessão, por disposição, de 06(seis) técnicos detentores de empregos do Quadro da PRODAM.</t>
+          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
         </is>
       </c>
     </row>
@@ -2502,7 +2514,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2015NE00602</t>
+          <t>2015NE00604</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2516,7 +2528,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>34138.41</v>
+        <v>6334.43</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2532,7 +2544,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2015NE00604</t>
+          <t>2015NE00602</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2546,7 +2558,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>6334.43</v>
+        <v>34138.41</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2588,17 +2600,21 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2022NE0001040</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
+          <t>2022NE0001035</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>4/2018</t>
+        </is>
+      </c>
       <c r="C74" t="inlineStr">
         <is>
           <t>23/08/2022</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>138503.52</v>
+        <v>53392.86</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2607,28 +2623,24 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada , por disposição da Prodam, dos técnicos detentores de empregos, conforme Projeto Básico.</t>
+          <t>Contratação de empresa especializada, para prestação de serviços de firewall, com acesso à Rede local, etc, conforme Projeto Básico.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2022NE0001035</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>4/2018</t>
-        </is>
-      </c>
+          <t>2022NE0001040</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
           <t>23/08/2022</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>53392.86</v>
+        <v>138503.52</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2637,7 +2649,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada, para prestação de serviços de firewall, com acesso à Rede local, etc, conforme Projeto Básico.</t>
+          <t>Contratação de empresa especializada , por disposição da Prodam, dos técnicos detentores de empregos, conforme Projeto Básico.</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2734,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2022NE0001265</t>
+          <t>2022NE0001266</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -2732,7 +2744,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>18109.3</v>
+        <v>15292.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2741,14 +2753,14 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DO SALDO DO TERMO DE CONVÊNIO Nº001/2021,</t>
+          <t>ANULAÇÃO PÁRCIAL DA NE Nº000027, TENDO EM VISTA O ENCERRAMENTO DO TERCEIRO TERMO ADITIVO, AO CONTRATO Nº004/2018.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2022NE0001266</t>
+          <t>2022NE0001265</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -2758,7 +2770,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>15292.5</v>
+        <v>18109.3</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2767,28 +2779,24 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PÁRCIAL DA NE Nº000027, TENDO EM VISTA O ENCERRAMENTO DO TERCEIRO TERMO ADITIVO, AO CONTRATO Nº004/2018.</t>
+          <t>ANULAÇÃO PARCIAL DO SALDO DO TERMO DE CONVÊNIO Nº001/2021,</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2016NE00428</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>3/2012</t>
-        </is>
-      </c>
+          <t>2016NE00437</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
           <t>22/11/2016</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>19150.1</v>
+        <v>65741.71000000001</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2797,7 +2805,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Serviço técnicos de telecomunicação de disponibilidade de acesso remoto a rede mundial de internet, gestão de redes locais e uso do SPROWEB, na Sede do Governo.</t>
+          <t>Referente a cessão por disposição da Prodam S.A. dos técnicos constantes no anexo 1 Convênio.</t>
         </is>
       </c>
     </row>
@@ -2834,17 +2842,21 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2016NE00437</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
+          <t>2016NE00428</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>3/2012</t>
+        </is>
+      </c>
       <c r="C83" t="inlineStr">
         <is>
           <t>22/11/2016</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>65741.71000000001</v>
+        <v>19150.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2853,7 +2865,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Referente a cessão por disposição da Prodam S.A. dos técnicos constantes no anexo 1 Convênio.</t>
+          <t>Serviço técnicos de telecomunicação de disponibilidade de acesso remoto a rede mundial de internet, gestão de redes locais e uso do SPROWEB, na Sede do Governo.</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2980,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2019NE00208</t>
+          <t>2019NE00195</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3020,7 +3032,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2019NE00195</t>
+          <t>2019NE00208</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3274,7 +3286,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2023NE0000572</t>
+          <t>2023NE0000571</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -3284,7 +3296,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>30850.29</v>
+        <v>17757.62</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3293,14 +3305,14 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NOTA DE EMPENHO Nº000005, EM RAZÃO DO TÉRMINO DO SEGUNDO TERMO ADITIVO AO CONVÊNIO Nº001/2021, ENCERRADO EM 01.05.2023.</t>
+          <t>ANULAÇÃO PARCIAL DA NOTA DE EMPENHO Nº000004, EM RAZÃO DO TÉRMINO DO QUARTO TERMO ADITIVO AO CONTRATO Nº004/2018, ENCERRADO EM 12.06.2023.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2023NE0000571</t>
+          <t>2023NE0000572</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -3310,7 +3322,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>17757.62</v>
+        <v>30850.29</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3319,7 +3331,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NOTA DE EMPENHO Nº000004, EM RAZÃO DO TÉRMINO DO QUARTO TERMO ADITIVO AO CONTRATO Nº004/2018, ENCERRADO EM 12.06.2023.</t>
+          <t>ANULAÇÃO PARCIAL DA NOTA DE EMPENHO Nº000005, EM RAZÃO DO TÉRMINO DO SEGUNDO TERMO ADITIVO AO CONVÊNIO Nº001/2021, ENCERRADO EM 01.05.2023.</t>
         </is>
       </c>
     </row>
@@ -3382,14 +3394,10 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2024NE0000591</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>3/2023</t>
-        </is>
-      </c>
+          <t>2024NE0000592</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
           <t>16/08/2024</t>
@@ -3405,17 +3413,21 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
+          <t>Anulação total da Nota de Empenho: 579/2024, para ajustes na fonte de recurso.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2024NE0000592</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr"/>
+          <t>2024NE0000591</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>3/2023</t>
+        </is>
+      </c>
       <c r="C104" t="inlineStr">
         <is>
           <t>16/08/2024</t>
@@ -3431,7 +3443,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Anulação total da Nota de Empenho: 579/2024, para ajustes na fonte de recurso.</t>
+          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
         </is>
       </c>
     </row>
@@ -3490,7 +3502,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2015NE00115</t>
+          <t>2015NE00123</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -3500,7 +3512,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1594.14</v>
+        <v>1929.73</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3516,7 +3528,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2015NE00123</t>
+          <t>2015NE00115</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -3526,7 +3538,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1929.73</v>
+        <v>1594.14</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3572,7 +3584,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2023NE0000442</t>
+          <t>2023NE00442</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3595,14 +3607,14 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
+          <t>Prestação de Serviços Gestor de Conteúdo Web, SPROWEB e Hospedagem de Servidor.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2023NE00442</t>
+          <t>2023NE0000442</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3625,7 +3637,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Prestação de Serviços Gestor de Conteúdo Web, SPROWEB e Hospedagem de Servidor.</t>
+          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
         </is>
       </c>
     </row>
@@ -4144,21 +4156,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026NE0000004</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>3/2023</t>
-        </is>
-      </c>
+          <t>2026NE0000003</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
           <t>05/01/2026</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>19138.4</v>
+        <v>438762.04</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4167,24 +4175,28 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
+          <t>Correspondente a cessão por disposição de 05(cinco) Técnicos detentores de empregos do Quadro da PRODAM.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026NE0000003</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
+          <t>2026NE0000004</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>3/2023</t>
+        </is>
+      </c>
       <c r="C131" t="inlineStr">
         <is>
           <t>05/01/2026</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>438762.04</v>
+        <v>19138.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4193,19 +4205,19 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Correspondente a cessão por disposição de 05(cinco) Técnicos detentores de empregos do Quadro da PRODAM.</t>
+          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2015NE00011</t>
+          <t>2015NE00012</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>3/2012</t>
+          <t>11/2013</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4214,7 +4226,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>59133.84</v>
+        <v>18197.01</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4230,12 +4242,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2015NE00012</t>
+          <t>2015NE00011</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>11/2013</t>
+          <t>3/2012</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4244,7 +4256,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>18197.01</v>
+        <v>59133.84</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4312,21 +4324,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2023NE0000537</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>3/2023</t>
-        </is>
-      </c>
+          <t>2023NE0000536</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
           <t>04/09/2023</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>4340.69</v>
+        <v>101717.66</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4335,24 +4343,28 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
+          <t>TERCEIRO TERMO ADITIVO AO CONVÊNIO Nº001/2021 OBJETO: O presente Termo Aditivo tem por objeto a prorrogação do prazo de vigência do Termo de Convênio nº001/2021, cujo objeto é a cessão, por disposição</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2023NE0000536</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
+          <t>2023NE0000537</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>3/2023</t>
+        </is>
+      </c>
       <c r="C137" t="inlineStr">
         <is>
           <t>04/09/2023</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>101717.66</v>
+        <v>4340.69</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4361,14 +4373,14 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>TERCEIRO TERMO ADITIVO AO CONVÊNIO Nº001/2021 OBJETO: O presente Termo Aditivo tem por objeto a prorrogação do prazo de vigência do Termo de Convênio nº001/2021, cujo objeto é a cessão, por disposição</t>
+          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2023NE0000276</t>
+          <t>2023NE00276</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -4387,14 +4399,14 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Contratação de empresa espécializada, cujo pbjeto a cessão, por disposição, de 06(seis) técnicos detentores do Quadro da PRODAM, para atender as necessidade da Casa Civil.</t>
+          <t>Cobertura Financeira do 3º Termo Aditivo ao Convênio 001/2021</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2023NE00276</t>
+          <t>2023NE0000276</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -4413,7 +4425,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Cobertura Financeira do 3º Termo Aditivo ao Convênio 001/2021</t>
+          <t>Contratação de empresa espécializada, cujo pbjeto a cessão, por disposição, de 06(seis) técnicos detentores do Quadro da PRODAM, para atender as necessidade da Casa Civil.</t>
         </is>
       </c>
     </row>
@@ -4472,12 +4484,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2019NE00224</t>
+          <t>2019NE00223</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>7/2018</t>
+          <t>4/2018</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4486,7 +4498,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>39701.28</v>
+        <v>45198.26</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4495,19 +4507,19 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Prestação de serviços de desenvolvimento de sistemas de informação, compreendendo a análise e desenvolvimento de funcionalidades, hospedagem de sistemas e suporte técnico para o protejo "Meu Amazonas,</t>
+          <t>Contratação de empresa especializada, por força deste Contrato a contratada obriga-se a prestar a Contratante os serviços de firewall, com disponibilização e administração de equipamentos; serviços de</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2019NE00223</t>
+          <t>2019NE00224</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>4/2018</t>
+          <t>7/2018</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4516,7 +4528,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>45198.26</v>
+        <v>39701.28</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -4525,28 +4537,24 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada, por força deste Contrato a contratada obriga-se a prestar a Contratante os serviços de firewall, com disponibilização e administração de equipamentos; serviços de</t>
+          <t>Prestação de serviços de desenvolvimento de sistemas de informação, compreendendo a análise e desenvolvimento de funcionalidades, hospedagem de sistemas e suporte técnico para o protejo "Meu Amazonas,</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2021NE0000030</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>4/2018</t>
-        </is>
-      </c>
+          <t>2021NE0000031</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
           <t>04/01/2021</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>81560.28</v>
+        <v>249135.72</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -4555,24 +4563,28 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada, por força deste Contrato a Contratada obriga-se a prestar a Contratante os serviços de firewall, c/disponib.e administ.equipamentos,serviços de rede, acesso geren</t>
+          <t>Para atender despesas com o Convênio Nº 001/2016, ref. a cessão de técnicos do quadro de técnicos da PRODAM pelo período de 4(quatro) meses.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2021NE0000031</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
+          <t>2021NE0000030</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>4/2018</t>
+        </is>
+      </c>
       <c r="C145" t="inlineStr">
         <is>
           <t>04/01/2021</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>249135.72</v>
+        <v>81560.28</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -4581,28 +4593,24 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Para atender despesas com o Convênio Nº 001/2016, ref. a cessão de técnicos do quadro de técnicos da PRODAM pelo período de 4(quatro) meses.</t>
+          <t>Contratação de empresa especializada, por força deste Contrato a Contratada obriga-se a prestar a Contratante os serviços de firewall, c/disponib.e administ.equipamentos,serviços de rede, acesso geren</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2016NE00063</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>11/2013</t>
-        </is>
-      </c>
+          <t>2016NE00034</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
           <t>04/01/2016</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>37886.16</v>
+        <v>113166.33</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -4611,14 +4619,14 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE INFORMÁTICA</t>
+          <t>Cessão, por disposição, da Prodam, dos técnicos constantes no Anexo I do Convênio nº001/2015.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2016NE00049</t>
+          <t>2016NE00024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4632,7 +4640,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>49434.06</v>
+        <v>66409.21000000001</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -4641,14 +4649,14 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestação dos serviços técnicos, em telecomunicações de disponibilidade de acesso remoto a rede mundial internet, com a velocidade dedicada de 5,5Mbps, gestão de redes locais(firewall UTM0 e a cessão </t>
+          <t>Contratos para Serviços de Informática</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2016NE00024</t>
+          <t>2016NE00049</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4662,7 +4670,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>66409.21000000001</v>
+        <v>49434.06</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -4671,24 +4679,28 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Contratos para Serviços de Informática</t>
+          <t xml:space="preserve">Prestação dos serviços técnicos, em telecomunicações de disponibilidade de acesso remoto a rede mundial internet, com a velocidade dedicada de 5,5Mbps, gestão de redes locais(firewall UTM0 e a cessão </t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2016NE00034</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr"/>
+          <t>2016NE00063</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>11/2013</t>
+        </is>
+      </c>
       <c r="C149" t="inlineStr">
         <is>
           <t>04/01/2016</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>113166.33</v>
+        <v>37886.16</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -4697,7 +4709,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Cessão, por disposição, da Prodam, dos técnicos constantes no Anexo I do Convênio nº001/2015.</t>
+          <t>SERVIÇOS DE INFORMÁTICA</t>
         </is>
       </c>
     </row>
@@ -4730,12 +4742,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2015NE00524</t>
+          <t>2015NE00521</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>11/2013</t>
+          <t>3/2012</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4744,7 +4756,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>4516.91</v>
+        <v>4138.73</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -4753,19 +4765,19 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Anulação parcial tendo em vista o valor do consumo ter sido menor que o valor programado.</t>
+          <t>Anulação parcial tendo em vista o término do Contrato nº003/2012.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2015NE00521</t>
+          <t>2015NE00524</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>3/2012</t>
+          <t>11/2013</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4774,7 +4786,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>4138.73</v>
+        <v>4516.91</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -4783,7 +4795,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Anulação parcial tendo em vista o término do Contrato nº003/2012.</t>
+          <t>Anulação parcial tendo em vista o valor do consumo ter sido menor que o valor programado.</t>
         </is>
       </c>
     </row>
@@ -4816,21 +4828,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2022NE0000027</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>4/2018</t>
-        </is>
-      </c>
+          <t>2022NE0000038</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
           <t>03/01/2022</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>91960.84</v>
+        <v>288012</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -4839,24 +4847,28 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada, por força deste Contrato a Contratada obriga-se a prestar a Contratante os serviços de firewall, c/disponib.e administ.equipamentos,serviços de rede, acesso geren</t>
+          <t>Correspondente a cessão por disposição da Prodam, dos Técnicos detentores de empregos, conforme Termo de Convênio nº001/2021.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2022NE0000038</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr"/>
+          <t>2022NE0000027</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>4/2018</t>
+        </is>
+      </c>
       <c r="C155" t="inlineStr">
         <is>
           <t>03/01/2022</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>288012</v>
+        <v>91960.84</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -4865,7 +4877,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Correspondente a cessão por disposição da Prodam, dos Técnicos detentores de empregos, conforme Termo de Convênio nº001/2021.</t>
+          <t>Contratação de empresa especializada, por força deste Contrato a Contratada obriga-se a prestar a Contratante os serviços de firewall, c/disponib.e administ.equipamentos,serviços de rede, acesso geren</t>
         </is>
       </c>
     </row>
@@ -5006,17 +5018,21 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2024NE0000006</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr"/>
+          <t>2024NE0000004</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>3/2023</t>
+        </is>
+      </c>
       <c r="C161" t="inlineStr">
         <is>
           <t>02/01/2024</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>223778.86</v>
+        <v>8681.379999999999</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5025,28 +5041,24 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Cessão, por disposição, de 06(seis) técnicos detentores de empregos do Quadro da PRODAM, referente aos meses de janeiro de fevereiro/2024.(3ºTA ao Convenio nº001/2021)</t>
+          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2024NE0000004</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>3/2023</t>
-        </is>
-      </c>
+          <t>2024NE0000006</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr">
         <is>
           <t>02/01/2024</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>8681.379999999999</v>
+        <v>223778.86</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5055,7 +5067,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
+          <t>Cessão, por disposição, de 06(seis) técnicos detentores de empregos do Quadro da PRODAM, referente aos meses de janeiro de fevereiro/2024.(3ºTA ao Convenio nº001/2021)</t>
         </is>
       </c>
     </row>
@@ -5088,17 +5100,21 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2020NE00020</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr"/>
+          <t>2020NE00018</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>4/2018</t>
+        </is>
+      </c>
       <c r="C164" t="inlineStr">
         <is>
           <t>02/01/2020</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>255391.4</v>
+        <v>110106.38</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5107,7 +5123,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Correspondente a cessão, por disposição, de técnicos detentores de empregos do Quadro de Técnicos da PRODAM - (Quarto Termo Aditivo ao Termo de Convênio nº001/2016.</t>
+          <t>Contratação de empresa especializada, por força deste Contrato a Contratada obriga-se a prestar a Contratante os serviços de firewall, com disponibilização e administração de equipamentos; serviços de</t>
         </is>
       </c>
     </row>
@@ -5140,21 +5156,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2020NE00018</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>4/2018</t>
-        </is>
-      </c>
+          <t>2020NE00020</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
           <t>02/01/2020</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>110106.38</v>
+        <v>255391.4</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5163,28 +5175,24 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada, por força deste Contrato a Contratada obriga-se a prestar a Contratante os serviços de firewall, com disponibilização e administração de equipamentos; serviços de</t>
+          <t>Correspondente a cessão, por disposição, de técnicos detentores de empregos do Quadro de Técnicos da PRODAM - (Quarto Termo Aditivo ao Termo de Convênio nº001/2016.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2019NE00005</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>7/2018</t>
-        </is>
-      </c>
+          <t>2019NE00014</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr">
         <is>
           <t>02/01/2019</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>154798.92</v>
+        <v>268385.58</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5193,7 +5201,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada para prestar serviços de desenvolvimento de sistemas de informação, compreendendo a análise e desenvolvimento de funcionalidades, hospedagem de sistemas e suporte </t>
+          <t>O Presente Termo Aditivo tem por objeto a prorrogação do prazo de vigência do termo de Convênio nº001/2016, assim como a cessão, por disposição de técnicos detentores de empregos do Quadro de Técnicos</t>
         </is>
       </c>
     </row>
@@ -5230,17 +5238,21 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2019NE00014</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr"/>
+          <t>2019NE00005</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>7/2018</t>
+        </is>
+      </c>
       <c r="C169" t="inlineStr">
         <is>
           <t>02/01/2019</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>268385.58</v>
+        <v>154798.92</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5249,24 +5261,28 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>O Presente Termo Aditivo tem por objeto a prorrogação do prazo de vigência do termo de Convênio nº001/2016, assim como a cessão, por disposição de técnicos detentores de empregos do Quadro de Técnicos</t>
+          <t xml:space="preserve">Contratação de empresa especializada para prestar serviços de desenvolvimento de sistemas de informação, compreendendo a análise e desenvolvimento de funcionalidades, hospedagem de sistemas e suporte </t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2018NE00066</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr"/>
+          <t>2018NE00073</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>3/2012</t>
+        </is>
+      </c>
       <c r="C170" t="inlineStr">
         <is>
           <t>02/01/2018</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>256317.05</v>
+        <v>73408.72</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5275,17 +5291,21 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Correspondente aos serviços prestados, por disposição (cessão), dos técnicos constantes no anexo 1 (um) deste Convênio.</t>
+          <t>Contratação de empresa especializada para prestação de serviços técnicos em telecomunicações de disponibilidade de acesso remoto à rede mundial internet, com velocidade 4,5 mbps, gestão de redes locai</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2018NE00075</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr"/>
+          <t>2018NE00076</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>3/2012</t>
+        </is>
+      </c>
       <c r="C171" t="inlineStr">
         <is>
           <t>02/01/2018</t>
@@ -5301,21 +5321,17 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Anulação total da NE nº00073, por ter informado o Programa de Trabalho incorreto.</t>
+          <t>Contratação de empresa especializada para prestação de serviços técnicos em telecomunicações de disponibilidade de acesso remoto à rede mundial internet, com velocidade 4,5 mbps, gestão de redes locai</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2018NE00076</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>3/2012</t>
-        </is>
-      </c>
+          <t>2018NE00075</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
         <is>
           <t>02/01/2018</t>
@@ -5331,28 +5347,24 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para prestação de serviços técnicos em telecomunicações de disponibilidade de acesso remoto à rede mundial internet, com velocidade 4,5 mbps, gestão de redes locai</t>
+          <t>Anulação total da NE nº00073, por ter informado o Programa de Trabalho incorreto.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2018NE00073</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>3/2012</t>
-        </is>
-      </c>
+          <t>2018NE00066</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
         <is>
           <t>02/01/2018</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>73408.72</v>
+        <v>256317.05</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5361,28 +5373,24 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada para prestação de serviços técnicos em telecomunicações de disponibilidade de acesso remoto à rede mundial internet, com velocidade 4,5 mbps, gestão de redes locai</t>
+          <t>Correspondente aos serviços prestados, por disposição (cessão), dos técnicos constantes no anexo 1 (um) deste Convênio.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2017NE00034</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>3/2012</t>
-        </is>
-      </c>
+          <t>2017NE00025</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr">
         <is>
           <t>02/01/2017</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>72770.38</v>
+        <v>264939.07</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -5391,19 +5399,19 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Contratação de prestação de serviços técnicos em telecomunicações de disponibilidade de acesso remoto à rede mundial internet, com velocidade 4,5 mbps, gestão de redes locais e a cessão de uso do Sist</t>
+          <t>O presente CONVÊNIO tem por objeto a CESSÃO, por disposição da PRODAM - Processamento de Dados Amazonas S/A, dos técnicos constantes no Anexo 1 deste documento</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2017NE00027</t>
+          <t>2017NE00038</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>10/2016</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5421,19 +5429,19 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização de gestor de conteúdo web ao Fundo de Promoção Social, para publicação de informação, </t>
+          <t>Contratação de prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização de gestor de conteúdo web da Casa Civil, para publicação de informação, notícias, víde</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2017NE00031</t>
+          <t>2017NE00033</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>11/2013</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5442,7 +5450,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>16523.4</v>
+        <v>50935.84</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -5451,7 +5459,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização de gestor de conteúdo web ao FPS, para publicação de informações, notícias, vídeos e</t>
+          <t xml:space="preserve">Contratação de prestação de serviços eventuais de informática, para a Sede do Governo do Estado do Amazonas e Prédio Anexo, pelo período de 12 meses, cuja descrição está contida no Projeto Básico que </t>
         </is>
       </c>
     </row>
@@ -5484,12 +5492,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2017NE00033</t>
+          <t>2017NE00031</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>11/2013</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5498,7 +5506,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>50935.84</v>
+        <v>16523.4</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -5507,19 +5515,19 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de prestação de serviços eventuais de informática, para a Sede do Governo do Estado do Amazonas e Prédio Anexo, pelo período de 12 meses, cuja descrição está contida no Projeto Básico que </t>
+          <t>Contratação para prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização de gestor de conteúdo web ao FPS, para publicação de informações, notícias, vídeos e</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2017NE00038</t>
+          <t>2017NE00027</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>10/2016</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5537,24 +5545,28 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Contratação de prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização de gestor de conteúdo web da Casa Civil, para publicação de informação, notícias, víde</t>
+          <t xml:space="preserve">Contratação de prestação de serviços de licença de uso de sistema de informação, compreendendo a disponibilização de gestor de conteúdo web ao Fundo de Promoção Social, para publicação de informação, </t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2017NE00025</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr"/>
+          <t>2017NE00034</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>3/2012</t>
+        </is>
+      </c>
       <c r="C180" t="inlineStr">
         <is>
           <t>02/01/2017</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>264939.07</v>
+        <v>72770.38</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -5563,19 +5575,19 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>O presente CONVÊNIO tem por objeto a CESSÃO, por disposição da PRODAM - Processamento de Dados Amazonas S/A, dos técnicos constantes no Anexo 1 deste documento</t>
+          <t>Contratação de prestação de serviços técnicos em telecomunicações de disponibilidade de acesso remoto à rede mundial internet, com velocidade 4,5 mbps, gestão de redes locais e a cessão de uso do Sist</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2014NE00034</t>
+          <t>2014NE00005</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>11/2013</t>
+          <t>3/2012</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5584,7 +5596,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>45675.2</v>
+        <v>70984.53999999999</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -5593,7 +5605,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Contrato No. 11/2013 - Serviços Eventuais em Informatica</t>
+          <t>Contrato No. 3/2012 - Acesso Internet, Firewall UTM, Sistema Protocolo - SPROWEB</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5642,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2014NE00005</t>
+          <t>2014NE00034</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>3/2012</t>
+          <t>11/2013</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5644,7 +5656,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>70984.53999999999</v>
+        <v>45675.2</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -5653,24 +5665,28 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Contrato No. 3/2012 - Acesso Internet, Firewall UTM, Sistema Protocolo - SPROWEB</t>
+          <t>Contrato No. 11/2013 - Serviços Eventuais em Informatica</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2016NE00501</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr"/>
+          <t>2016NE00499</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>3/2012</t>
+        </is>
+      </c>
       <c r="C184" t="inlineStr">
         <is>
           <t>01/12/2016</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>65741.71000000001</v>
+        <v>19150.1</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -5679,7 +5695,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Correspondente a cessão, por disposição da Prodam S/A, dos técnicos constante no anexo 1 do convênio.</t>
+          <t>Serviço técnicos de telecomunicação de disponibilidade de acesso remoto a rede mundial de internet, gestão de redes locais e uso do SPROWEB, na Sede do Governo.</t>
         </is>
       </c>
     </row>
@@ -5716,21 +5732,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2016NE00499</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>3/2012</t>
-        </is>
-      </c>
+          <t>2016NE00501</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
       <c r="C186" t="inlineStr">
         <is>
           <t>01/12/2016</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>19150.1</v>
+        <v>65741.71000000001</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -5739,7 +5751,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Serviço técnicos de telecomunicação de disponibilidade de acesso remoto a rede mundial de internet, gestão de redes locais e uso do SPROWEB, na Sede do Governo.</t>
+          <t>Correspondente a cessão, por disposição da Prodam S/A, dos técnicos constante no anexo 1 do convênio.</t>
         </is>
       </c>
     </row>
@@ -5806,17 +5818,21 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2024NE0000445</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr"/>
+          <t>2024NE0000448</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>3/2023</t>
+        </is>
+      </c>
       <c r="C189" t="inlineStr">
         <is>
           <t>01/07/2024</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>203435.32</v>
+        <v>1512</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -5825,7 +5841,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Cessão, por disposição, de 06 (seis) Técnicos detentores de empregos do Quadro da PRODAM</t>
+          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
         </is>
       </c>
     </row>
@@ -5862,21 +5878,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2024NE0000448</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>3/2023</t>
-        </is>
-      </c>
+          <t>2024NE0000445</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
       <c r="C191" t="inlineStr">
         <is>
           <t>01/07/2024</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1512</v>
+        <v>203435.32</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -5885,7 +5897,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada, para fornecimento de licença de uso de Sistema de Informação, disponibilizando o Gestor de Conteúdo Web - GERWEB para publicação de informações, notícias, vídeos </t>
+          <t>Cessão, por disposição, de 06 (seis) Técnicos detentores de empregos do Quadro da PRODAM</t>
         </is>
       </c>
     </row>
@@ -5948,12 +5960,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2015NE00352</t>
+          <t>2015NE00354</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>3/2012</t>
+          <t>11/2013</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5962,7 +5974,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>16426.07</v>
+        <v>30732.66</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -5971,19 +5983,19 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015. Proporcional a 24 dias de abril</t>
+          <t>reforço do empenho</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2015NE00354</t>
+          <t>2015NE00352</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>11/2013</t>
+          <t>3/2012</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5992,7 +6004,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>30732.66</v>
+        <v>16426.07</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6001,7 +6013,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>reforço do empenho</t>
+          <t>Cobertura Financeira 2015. Proporcional a 24 dias de abril</t>
         </is>
       </c>
     </row>

--- a/DOSSIES_MULTIFORMATO/CASA_CIVIL/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/CASA_CIVIL/dossie.xlsx
@@ -565,7 +565,11 @@
           <t>data_prescricao_proxima</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2031-03-31</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
